--- a/reports/excel/MacroPulse_2026-07-09.xlsx
+++ b/reports/excel/MacroPulse_2026-07-09.xlsx
@@ -651,7 +651,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MacroPulse 總體經濟指標報告　　生成時間：2026-07-09 15:40 UTC</t>
+          <t>MacroPulse 總體經濟指標報告　　生成時間：2026-07-09 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -2429,17 +2429,17 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
+          <t>+0.190 pp</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>YoY (pp)</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
           <t>+0.060 pp</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>YoY (pp)</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -2866,7 +2866,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🔥 通膨指標　歷史數據　　生成時間：2026-07-09 15:40 UTC</t>
+          <t>🔥 通膨指標　歷史數據　　生成時間：2026-07-09 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14688,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>📈 經濟成長　歷史數據　　生成時間：2026-07-09 15:40 UTC</t>
+          <t>📈 經濟成長　歷史數據　　生成時間：2026-07-09 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -24692,7 +24692,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>👷 勞動市場　歷史數據　　生成時間：2026-07-09 15:40 UTC</t>
+          <t>👷 勞動市場　歷史數據　　生成時間：2026-07-09 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -36517,7 +36517,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🏦 利率與債券　歷史數據　　生成時間：2026-07-09 15:40 UTC</t>
+          <t>🏦 利率與債券　歷史數據　　生成時間：2026-07-09 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -36658,7 +36658,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
@@ -36738,7 +36738,7 @@
       </c>
       <c r="Q4" s="19" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="R4" s="19" t="inlineStr">
@@ -36748,14 +36748,14 @@
       </c>
       <c r="S4" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -36835,7 +36835,7 @@
       </c>
       <c r="Q5" s="20" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="R5" s="20" t="inlineStr">
@@ -36845,94 +36845,94 @@
       </c>
       <c r="S5" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.200 pp</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.200 pp</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.400 pp</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.350 pp</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.660 pp</t>
         </is>
       </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="L6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.430 pp</t>
         </is>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>+0.740 pp</t>
         </is>
       </c>
       <c r="P6" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="Q6" s="19" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R6" s="19" t="inlineStr">
@@ -36942,94 +36942,94 @@
       </c>
       <c r="S6" s="19" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>-0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>-0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>-1.400 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>-0.350 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>-0.660 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
         <is>
-          <t>-0.430 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O7" s="12" t="inlineStr">
-        <is>
-          <t>+0.740 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P7" s="20" t="inlineStr">
         <is>
-          <t>+0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="R7" s="20" t="inlineStr">
@@ -37039,14 +37039,14 @@
       </c>
       <c r="S7" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -37126,7 +37126,7 @@
       </c>
       <c r="Q8" s="19" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="R8" s="19" t="inlineStr">
@@ -37136,14 +37136,14 @@
       </c>
       <c r="S8" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -37223,7 +37223,7 @@
       </c>
       <c r="Q9" s="20" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="R9" s="20" t="inlineStr">
@@ -37233,14 +37233,14 @@
       </c>
       <c r="S9" s="20" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
@@ -37320,7 +37320,7 @@
       </c>
       <c r="Q10" s="19" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="R10" s="19" t="inlineStr">
@@ -37330,94 +37330,94 @@
       </c>
       <c r="S10" s="19" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.500 pp</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.300 pp</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.100 pp</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.350 pp</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.700 pp</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.380 pp</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.570 pp</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.340 pp</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>+0.390 pp</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R11" s="20" t="inlineStr">
@@ -37427,94 +37427,94 @@
       </c>
       <c r="S11" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>-0.500 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>-0.300 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>-1.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>+0.350 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
-          <t>-0.700 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>+0.380 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="19" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="19" t="inlineStr">
         <is>
-          <t>-0.570 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M12" s="19" t="inlineStr">
         <is>
-          <t>+0.340 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="O12" s="9" t="inlineStr">
-        <is>
-          <t>+0.390 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P12" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="R12" s="19" t="inlineStr">
@@ -37524,14 +37524,14 @@
       </c>
       <c r="S12" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -37611,24 +37611,24 @@
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="R13" s="20" t="inlineStr">
         <is>
-          <t>-0.770 pp</t>
+          <t>-0.450 pp</t>
         </is>
       </c>
       <c r="S13" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>+0.200 pp</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
@@ -37708,24 +37708,24 @@
       </c>
       <c r="Q14" s="19" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="R14" s="19" t="inlineStr">
         <is>
-          <t>-0.450 pp</t>
+          <t>-0.340 pp</t>
         </is>
       </c>
       <c r="S14" s="19" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>+0.120 pp</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -37805,24 +37805,24 @@
       </c>
       <c r="Q15" s="20" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="R15" s="20" t="inlineStr">
         <is>
-          <t>-0.340 pp</t>
+          <t>-0.190 pp</t>
         </is>
       </c>
       <c r="S15" s="20" t="inlineStr">
         <is>
-          <t>+0.120 pp</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
@@ -37902,218 +37902,218 @@
       </c>
       <c r="Q16" s="19" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>-0.190 pp</t>
+          <t>+0.250 pp</t>
         </is>
       </c>
       <c r="S16" s="19" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>+0.180 pp</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.190 pp</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.620 pp</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.290 pp</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.140 pp</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.260 pp</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>+0.480 pp</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
       <c r="Q17" s="20" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R17" s="20" t="inlineStr">
         <is>
-          <t>+0.250 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S17" s="20" t="inlineStr">
         <is>
-          <t>+0.180 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>-0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>-0.620 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>+0.290 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>-0.140 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>+0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K18" s="19" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L18" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M18" s="19" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O18" s="9" t="inlineStr">
-        <is>
-          <t>+0.480 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q18" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="R18" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="S18" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -38193,24 +38193,24 @@
       </c>
       <c r="Q19" s="20" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="R19" s="20" t="inlineStr">
         <is>
-          <t>+0.300 pp</t>
+          <t>+0.320 pp</t>
         </is>
       </c>
       <c r="S19" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -38290,24 +38290,24 @@
       </c>
       <c r="Q20" s="19" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="R20" s="19" t="inlineStr">
         <is>
-          <t>+0.320 pp</t>
+          <t>+0.490 pp</t>
         </is>
       </c>
       <c r="S20" s="19" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -38387,218 +38387,218 @@
       </c>
       <c r="Q21" s="20" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="R21" s="20" t="inlineStr">
         <is>
-          <t>+0.490 pp</t>
+          <t>+0.460 pp</t>
         </is>
       </c>
       <c r="S21" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.850 pp</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.160 pp</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.230 pp</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.370 pp</t>
         </is>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="K22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="L22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.440 pp</t>
         </is>
       </c>
       <c r="M22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>+0.610 pp</t>
         </is>
       </c>
       <c r="P22" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="Q22" s="19" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R22" s="19" t="inlineStr">
         <is>
-          <t>+0.460 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S22" s="19" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>-0.850 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>-0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>-0.230 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>+0.370 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>+0.440 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
         <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="O23" s="12" t="inlineStr">
-        <is>
-          <t>+0.610 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="R23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.490 pp</t>
         </is>
       </c>
       <c r="S23" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
@@ -38678,24 +38678,24 @@
       </c>
       <c r="Q24" s="19" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>+0.490 pp</t>
+          <t>+0.510 pp</t>
         </is>
       </c>
       <c r="S24" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -38775,24 +38775,24 @@
       </c>
       <c r="Q25" s="20" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="R25" s="20" t="inlineStr">
         <is>
-          <t>+0.510 pp</t>
+          <t>+0.640 pp</t>
         </is>
       </c>
       <c r="S25" s="20" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>+0.120 pp</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
@@ -38872,218 +38872,218 @@
       </c>
       <c r="Q26" s="19" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="R26" s="19" t="inlineStr">
         <is>
-          <t>+0.640 pp</t>
+          <t>+0.730 pp</t>
         </is>
       </c>
       <c r="S26" s="19" t="inlineStr">
         <is>
-          <t>+0.120 pp</t>
+          <t>+0.130 pp</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.570 pp</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.590 pp</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.270 pp</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>+0.620 pp</t>
         </is>
       </c>
       <c r="P27" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="Q27" s="20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R27" s="20" t="inlineStr">
         <is>
-          <t>+0.730 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S27" s="20" t="inlineStr">
         <is>
-          <t>+0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>+0.570 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J28" s="19" t="inlineStr">
         <is>
-          <t>+0.240 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K28" s="19" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L28" s="19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="19" t="inlineStr">
+        <is>
+          <t>6.91</t>
+        </is>
+      </c>
+      <c r="R28" s="19" t="inlineStr">
+        <is>
           <t>+0.590 pp</t>
         </is>
       </c>
-      <c r="M28" s="19" t="inlineStr">
-        <is>
-          <t>+0.270 pp</t>
-        </is>
-      </c>
-      <c r="N28" s="19" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="O28" s="12" t="inlineStr">
-        <is>
-          <t>+0.620 pp</t>
-        </is>
-      </c>
-      <c r="P28" s="19" t="inlineStr">
-        <is>
-          <t>+0.190 pp</t>
-        </is>
-      </c>
-      <c r="Q28" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="S28" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -39163,24 +39163,24 @@
       </c>
       <c r="Q29" s="20" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="R29" s="20" t="inlineStr">
         <is>
-          <t>+0.590 pp</t>
+          <t>+0.490 pp</t>
         </is>
       </c>
       <c r="S29" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -39260,24 +39260,24 @@
       </c>
       <c r="Q30" s="19" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="R30" s="19" t="inlineStr">
         <is>
-          <t>+0.490 pp</t>
+          <t>+0.500 pp</t>
         </is>
       </c>
       <c r="S30" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>+0.110 pp</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -39357,24 +39357,24 @@
       </c>
       <c r="Q31" s="20" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="R31" s="20" t="inlineStr">
         <is>
-          <t>+0.500 pp</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="S31" s="20" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -39454,218 +39454,218 @@
       </c>
       <c r="Q32" s="19" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="R32" s="19" t="inlineStr">
         <is>
-          <t>+0.240 pp</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="S32" s="19" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.330 pp</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.180 pp</t>
         </is>
       </c>
       <c r="K33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="M33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.170 pp</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O33" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>+0.580 pp</t>
         </is>
       </c>
       <c r="P33" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R33" s="20" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S33" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>-0.330 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P34" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q34" s="19" t="inlineStr">
+        <is>
+          <t>6.89</t>
+        </is>
+      </c>
+      <c r="R34" s="19" t="inlineStr">
+        <is>
+          <t>+0.110 pp</t>
+        </is>
+      </c>
+      <c r="S34" s="19" t="inlineStr">
+        <is>
           <t>-0.060 pp</t>
-        </is>
-      </c>
-      <c r="H34" s="19" t="inlineStr">
-        <is>
-          <t>4.45</t>
-        </is>
-      </c>
-      <c r="I34" s="19" t="inlineStr">
-        <is>
-          <t>+0.240 pp</t>
-        </is>
-      </c>
-      <c r="J34" s="19" t="inlineStr">
-        <is>
-          <t>-0.180 pp</t>
-        </is>
-      </c>
-      <c r="K34" s="19" t="inlineStr">
-        <is>
-          <t>4.68</t>
-        </is>
-      </c>
-      <c r="L34" s="19" t="inlineStr">
-        <is>
-          <t>+0.300 pp</t>
-        </is>
-      </c>
-      <c r="M34" s="19" t="inlineStr">
-        <is>
-          <t>-0.170 pp</t>
-        </is>
-      </c>
-      <c r="N34" s="19" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="O34" s="12" t="inlineStr">
-        <is>
-          <t>+0.580 pp</t>
-        </is>
-      </c>
-      <c r="P34" s="19" t="inlineStr">
-        <is>
-          <t>-0.120 pp</t>
-        </is>
-      </c>
-      <c r="Q34" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R34" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S34" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -39745,24 +39745,24 @@
       </c>
       <c r="Q35" s="20" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="R35" s="20" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="S35" s="20" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="23" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
@@ -39842,12 +39842,12 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="R36" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="S36" s="19" t="inlineStr">
@@ -39859,7 +39859,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -39939,218 +39939,218 @@
       </c>
       <c r="Q37" s="20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="R37" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="S37" s="20" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.620 pp</t>
         </is>
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.240 pp</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="I38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="J38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.170 pp</t>
         </is>
       </c>
       <c r="K38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="L38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="M38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O38" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>+0.690 pp</t>
         </is>
       </c>
       <c r="P38" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="Q38" s="19" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R38" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S38" s="19" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>-0.620 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr">
         <is>
-          <t>-0.240 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H39" s="20" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J39" s="20" t="inlineStr">
         <is>
-          <t>-0.170 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K39" s="20" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L39" s="20" t="inlineStr">
         <is>
-          <t>+0.240 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M39" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="O39" s="12" t="inlineStr">
-        <is>
-          <t>+0.690 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O39" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P39" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="R39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="S39" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="23" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
@@ -40230,24 +40230,24 @@
       </c>
       <c r="Q40" s="19" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="R40" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>-0.070 pp</t>
         </is>
       </c>
       <c r="S40" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -40327,12 +40327,12 @@
       </c>
       <c r="Q41" s="20" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="R41" s="20" t="inlineStr">
         <is>
-          <t>-0.070 pp</t>
+          <t>-0.180 pp</t>
         </is>
       </c>
       <c r="S41" s="20" t="inlineStr">
@@ -40344,7 +40344,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
@@ -40424,218 +40424,218 @@
       </c>
       <c r="Q42" s="19" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="R42" s="19" t="inlineStr">
         <is>
-          <t>-0.180 pp</t>
+          <t>-0.260 pp</t>
         </is>
       </c>
       <c r="S42" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.090 pp</t>
         </is>
       </c>
       <c r="G43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.190 pp</t>
         </is>
       </c>
       <c r="H43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.260 pp</t>
         </is>
       </c>
       <c r="J43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="K43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="L43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
       <c r="M43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.110 pp</t>
         </is>
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O43" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>+0.830 pp</t>
         </is>
       </c>
       <c r="P43" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="Q43" s="20" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R43" s="20" t="inlineStr">
         <is>
-          <t>-0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S43" s="20" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>-1.090 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>-0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>-0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L44" s="19" t="inlineStr">
         <is>
-          <t>+0.050 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M44" s="19" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O44" s="12" t="inlineStr">
-        <is>
-          <t>+0.830 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O44" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P44" s="19" t="inlineStr">
         <is>
-          <t>+0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="R44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.290 pp</t>
         </is>
       </c>
       <c r="S44" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -40715,24 +40715,24 @@
       </c>
       <c r="Q45" s="20" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="R45" s="20" t="inlineStr">
         <is>
-          <t>-0.290 pp</t>
+          <t>-0.420 pp</t>
         </is>
       </c>
       <c r="S45" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="23" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
@@ -40812,24 +40812,24 @@
       </c>
       <c r="Q46" s="19" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="R46" s="19" t="inlineStr">
         <is>
-          <t>-0.420 pp</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="S46" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>+0.210 pp</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -40909,218 +40909,218 @@
       </c>
       <c r="Q47" s="20" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="R47" s="20" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>-0.140 pp</t>
         </is>
       </c>
       <c r="S47" s="20" t="inlineStr">
         <is>
-          <t>+0.210 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="23" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.940 pp</t>
         </is>
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.140 pp</t>
         </is>
       </c>
       <c r="H48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="J48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.140 pp</t>
         </is>
       </c>
       <c r="K48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="L48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.280 pp</t>
         </is>
       </c>
       <c r="M48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O48" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>+0.870 pp</t>
         </is>
       </c>
       <c r="P48" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="Q48" s="19" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="R48" s="19" t="inlineStr">
         <is>
-          <t>-0.140 pp</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="S48" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P49" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q49" s="20" t="inlineStr">
+        <is>
+          <t>6.76</t>
+        </is>
+      </c>
+      <c r="R49" s="20" t="inlineStr">
+        <is>
+          <t>-0.110 pp</t>
+        </is>
+      </c>
+      <c r="S49" s="20" t="inlineStr">
+        <is>
           <t>+0.000 pp</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>-0.940 pp</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="inlineStr">
-        <is>
-          <t>+0.140 pp</t>
-        </is>
-      </c>
-      <c r="H49" s="20" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="I49" s="20" t="inlineStr">
-        <is>
-          <t>-0.060 pp</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
-        <is>
-          <t>+0.140 pp</t>
-        </is>
-      </c>
-      <c r="K49" s="20" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="L49" s="20" t="inlineStr">
-        <is>
-          <t>+0.280 pp</t>
-        </is>
-      </c>
-      <c r="M49" s="20" t="inlineStr">
-        <is>
-          <t>+0.190 pp</t>
-        </is>
-      </c>
-      <c r="N49" s="20" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="O49" s="12" t="inlineStr">
-        <is>
-          <t>+0.870 pp</t>
-        </is>
-      </c>
-      <c r="P49" s="20" t="inlineStr">
-        <is>
-          <t>+0.000 pp</t>
-        </is>
-      </c>
-      <c r="Q49" s="20" t="inlineStr">
-        <is>
-          <t>6.76</t>
-        </is>
-      </c>
-      <c r="R49" s="20" t="inlineStr">
-        <is>
-          <t>-0.130 pp</t>
-        </is>
-      </c>
-      <c r="S49" s="20" t="inlineStr">
-        <is>
-          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
@@ -41200,24 +41200,24 @@
       </c>
       <c r="Q50" s="19" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="R50" s="19" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
       <c r="S50" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
@@ -41297,12 +41297,12 @@
       </c>
       <c r="Q51" s="20" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="R51" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="S51" s="20" t="inlineStr">
@@ -41314,7 +41314,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="23" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
@@ -41394,218 +41394,218 @@
       </c>
       <c r="Q52" s="19" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="R52" s="19" t="inlineStr">
         <is>
-          <t>+0.100 pp</t>
+          <t>+0.260 pp</t>
         </is>
       </c>
       <c r="S52" s="19" t="inlineStr">
         <is>
-          <t>+0.050 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.850 pp</t>
         </is>
       </c>
       <c r="G53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="H53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="I53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="J53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
       <c r="K53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="L53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.450 pp</t>
         </is>
       </c>
       <c r="M53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="N53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O53" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>+0.920 pp</t>
         </is>
       </c>
       <c r="P53" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="Q53" s="20" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R53" s="20" t="inlineStr">
         <is>
-          <t>+0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S53" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
-          <t>-0.850 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G54" s="19" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H54" s="19" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I54" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J54" s="19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K54" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L54" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M54" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N54" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O54" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P54" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q54" s="19" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="R54" s="19" t="inlineStr">
+        <is>
+          <t>+0.200 pp</t>
+        </is>
+      </c>
+      <c r="S54" s="19" t="inlineStr">
+        <is>
           <t>-0.040 pp</t>
-        </is>
-      </c>
-      <c r="K54" s="19" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="L54" s="19" t="inlineStr">
-        <is>
-          <t>+0.450 pp</t>
-        </is>
-      </c>
-      <c r="M54" s="19" t="inlineStr">
-        <is>
-          <t>-0.010 pp</t>
-        </is>
-      </c>
-      <c r="N54" s="19" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="O54" s="12" t="inlineStr">
-        <is>
-          <t>+0.920 pp</t>
-        </is>
-      </c>
-      <c r="P54" s="19" t="inlineStr">
-        <is>
-          <t>-0.010 pp</t>
-        </is>
-      </c>
-      <c r="Q54" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R54" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S54" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
@@ -41685,24 +41685,24 @@
       </c>
       <c r="Q55" s="20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="R55" s="20" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>+0.170 pp</t>
         </is>
       </c>
       <c r="S55" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="23" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
@@ -41782,24 +41782,24 @@
       </c>
       <c r="Q56" s="19" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="R56" s="19" t="inlineStr">
         <is>
-          <t>+0.170 pp</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="S56" s="19" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
@@ -41879,218 +41879,218 @@
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="R57" s="20" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>+0.130 pp</t>
         </is>
       </c>
       <c r="S57" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="23" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.620 pp</t>
         </is>
       </c>
       <c r="G58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="I58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.140 pp</t>
         </is>
       </c>
       <c r="J58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
       <c r="K58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="L58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.460 pp</t>
         </is>
       </c>
       <c r="M58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O58" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>+0.760 pp</t>
         </is>
       </c>
       <c r="P58" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
       <c r="Q58" s="19" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R58" s="19" t="inlineStr">
         <is>
-          <t>+0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S58" s="19" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>-0.620 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G59" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>+0.140 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J59" s="20" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L59" s="20" t="inlineStr">
         <is>
-          <t>+0.460 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M59" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N59" s="20" t="inlineStr">
         <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="O59" s="12" t="inlineStr">
-        <is>
-          <t>+0.760 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O59" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P59" s="20" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="R59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
       <c r="S59" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="23" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
@@ -42170,24 +42170,24 @@
       </c>
       <c r="Q60" s="19" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="R60" s="19" t="inlineStr">
         <is>
+          <t>-0.110 pp</t>
+        </is>
+      </c>
+      <c r="S60" s="19" t="inlineStr">
+        <is>
           <t>+0.050 pp</t>
-        </is>
-      </c>
-      <c r="S60" s="19" t="inlineStr">
-        <is>
-          <t>-0.100 pp</t>
         </is>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
@@ -42267,24 +42267,24 @@
       </c>
       <c r="Q61" s="20" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="R61" s="20" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="S61" s="20" t="inlineStr">
         <is>
-          <t>+0.050 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="23" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
@@ -42364,24 +42364,24 @@
       </c>
       <c r="Q62" s="19" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="R62" s="19" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
       <c r="S62" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
@@ -42461,218 +42461,218 @@
       </c>
       <c r="Q63" s="20" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="R63" s="20" t="inlineStr">
         <is>
+          <t>-0.040 pp</t>
+        </is>
+      </c>
+      <c r="S63" s="20" t="inlineStr">
+        <is>
           <t>-0.020 pp</t>
-        </is>
-      </c>
-      <c r="S63" s="20" t="inlineStr">
-        <is>
-          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="23" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-1.000 pp</t>
         </is>
       </c>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.270 pp</t>
         </is>
       </c>
       <c r="G64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.180 pp</t>
         </is>
       </c>
       <c r="H64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.390 pp</t>
         </is>
       </c>
       <c r="J64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="K64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="L64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.720 pp</t>
         </is>
       </c>
       <c r="M64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O64" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>+0.650 pp</t>
         </is>
       </c>
       <c r="P64" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
       <c r="Q64" s="19" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R64" s="19" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S64" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="23" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>-1.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>-0.270 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G65" s="20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P65" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q65" s="20" t="inlineStr">
+        <is>
+          <t>6.63</t>
+        </is>
+      </c>
+      <c r="R65" s="20" t="inlineStr">
+        <is>
           <t>-0.180 pp</t>
         </is>
       </c>
-      <c r="H65" s="20" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="I65" s="20" t="inlineStr">
-        <is>
-          <t>+0.390 pp</t>
-        </is>
-      </c>
-      <c r="J65" s="20" t="inlineStr">
-        <is>
-          <t>-0.130 pp</t>
-        </is>
-      </c>
-      <c r="K65" s="20" t="inlineStr">
-        <is>
-          <t>4.87</t>
-        </is>
-      </c>
-      <c r="L65" s="20" t="inlineStr">
-        <is>
-          <t>+0.720 pp</t>
-        </is>
-      </c>
-      <c r="M65" s="20" t="inlineStr">
-        <is>
-          <t>-0.050 pp</t>
-        </is>
-      </c>
-      <c r="N65" s="20" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="O65" s="12" t="inlineStr">
-        <is>
-          <t>+0.650 pp</t>
-        </is>
-      </c>
-      <c r="P65" s="20" t="inlineStr">
-        <is>
-          <t>+0.050 pp</t>
-        </is>
-      </c>
-      <c r="Q65" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R65" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="S65" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="23" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
@@ -42752,24 +42752,24 @@
       </c>
       <c r="Q66" s="19" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="R66" s="19" t="inlineStr">
         <is>
-          <t>-0.180 pp</t>
+          <t>-0.280 pp</t>
         </is>
       </c>
       <c r="S66" s="19" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B67" s="20" t="inlineStr">
@@ -42854,19 +42854,19 @@
       </c>
       <c r="R67" s="20" t="inlineStr">
         <is>
-          <t>-0.280 pp</t>
+          <t>-0.310 pp</t>
         </is>
       </c>
       <c r="S67" s="20" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
@@ -42946,218 +42946,218 @@
       </c>
       <c r="Q68" s="19" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="R68" s="19" t="inlineStr">
         <is>
-          <t>-0.310 pp</t>
+          <t>-0.290 pp</t>
         </is>
       </c>
       <c r="S68" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.910 pp</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="G69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="H69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.400 pp</t>
         </is>
       </c>
       <c r="J69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.140 pp</t>
         </is>
       </c>
       <c r="K69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="L69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.700 pp</t>
         </is>
       </c>
       <c r="M69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O69" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="O69" s="9" t="inlineStr">
+        <is>
+          <t>+0.450 pp</t>
         </is>
       </c>
       <c r="P69" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="Q69" s="20" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R69" s="20" t="inlineStr">
         <is>
-          <t>-0.290 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S69" s="20" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="23" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C70" s="19" t="inlineStr">
         <is>
-          <t>-0.910 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D70" s="19" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F70" s="19" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H70" s="19" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I70" s="19" t="inlineStr">
         <is>
-          <t>+0.400 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J70" s="19" t="inlineStr">
         <is>
-          <t>-0.140 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K70" s="19" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L70" s="19" t="inlineStr">
         <is>
-          <t>+0.700 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M70" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="O70" s="9" t="inlineStr">
-        <is>
-          <t>+0.450 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O70" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P70" s="19" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="R70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.340 pp</t>
         </is>
       </c>
       <c r="S70" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="23" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B71" s="20" t="inlineStr">
@@ -43237,24 +43237,24 @@
       </c>
       <c r="Q71" s="20" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="R71" s="20" t="inlineStr">
         <is>
-          <t>-0.340 pp</t>
+          <t>-0.460 pp</t>
         </is>
       </c>
       <c r="S71" s="20" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="23" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
@@ -43334,24 +43334,24 @@
       </c>
       <c r="Q72" s="19" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="R72" s="19" t="inlineStr">
         <is>
-          <t>-0.460 pp</t>
+          <t>-0.510 pp</t>
         </is>
       </c>
       <c r="S72" s="19" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B73" s="20" t="inlineStr">
@@ -43431,218 +43431,218 @@
       </c>
       <c r="Q73" s="20" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="R73" s="20" t="inlineStr">
         <is>
-          <t>-0.510 pp</t>
+          <t>-0.370 pp</t>
         </is>
       </c>
       <c r="S73" s="20" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="23" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="C74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.740 pp</t>
         </is>
       </c>
       <c r="D74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.450 pp</t>
         </is>
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="I74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
       <c r="J74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
       <c r="K74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="L74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.260 pp</t>
         </is>
       </c>
       <c r="M74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O74" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="inlineStr">
+        <is>
+          <t>+0.420 pp</t>
         </is>
       </c>
       <c r="P74" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="Q74" s="19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R74" s="19" t="inlineStr">
         <is>
-          <t>-0.370 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S74" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="23" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>-0.740 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>-0.450 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G75" s="20" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>-0.060 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K75" s="20" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L75" s="20" t="inlineStr">
         <is>
-          <t>+0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M75" s="20" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N75" s="20" t="inlineStr">
         <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="O75" s="9" t="inlineStr">
-        <is>
-          <t>+0.420 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O75" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P75" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="R75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.380 pp</t>
         </is>
       </c>
       <c r="S75" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="23" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
@@ -43722,24 +43722,24 @@
       </c>
       <c r="Q76" s="19" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="R76" s="19" t="inlineStr">
         <is>
-          <t>-0.380 pp</t>
+          <t>-0.450 pp</t>
         </is>
       </c>
       <c r="S76" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="23" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B77" s="20" t="inlineStr">
@@ -43819,24 +43819,24 @@
       </c>
       <c r="Q77" s="20" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="R77" s="20" t="inlineStr">
         <is>
-          <t>-0.450 pp</t>
+          <t>-0.470 pp</t>
         </is>
       </c>
       <c r="S77" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="23" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
@@ -43916,24 +43916,24 @@
       </c>
       <c r="Q78" s="19" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="R78" s="19" t="inlineStr">
         <is>
-          <t>-0.470 pp</t>
+          <t>-0.530 pp</t>
         </is>
       </c>
       <c r="S78" s="19" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B79" s="20" t="inlineStr">
@@ -44013,218 +44013,218 @@
       </c>
       <c r="Q79" s="20" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="R79" s="20" t="inlineStr">
         <is>
-          <t>-0.530 pp</t>
+          <t>-0.460 pp</t>
         </is>
       </c>
       <c r="S79" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="23" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="C80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.760 pp</t>
         </is>
       </c>
       <c r="D80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.210 pp</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.710 pp</t>
         </is>
       </c>
       <c r="G80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="I80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.270 pp</t>
         </is>
       </c>
       <c r="J80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="K80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="L80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="M80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O80" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="O80" s="9" t="inlineStr">
+        <is>
+          <t>+0.440 pp</t>
         </is>
       </c>
       <c r="P80" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="Q80" s="19" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R80" s="19" t="inlineStr">
         <is>
-          <t>-0.460 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S80" s="19" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>-0.760 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>-0.210 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>-0.710 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G81" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>-0.270 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K81" s="20" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L81" s="20" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M81" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="O81" s="9" t="inlineStr">
-        <is>
-          <t>+0.440 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O81" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P81" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q81" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="R81" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.360 pp</t>
         </is>
       </c>
       <c r="S81" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="23" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
@@ -44304,24 +44304,24 @@
       </c>
       <c r="Q82" s="19" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="R82" s="19" t="inlineStr">
         <is>
-          <t>-0.360 pp</t>
+          <t>-0.340 pp</t>
         </is>
       </c>
       <c r="S82" s="19" t="inlineStr">
         <is>
-          <t>+0.050 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B83" s="20" t="inlineStr">
@@ -44401,12 +44401,12 @@
       </c>
       <c r="Q83" s="20" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="R83" s="20" t="inlineStr">
         <is>
-          <t>-0.340 pp</t>
+          <t>-0.300 pp</t>
         </is>
       </c>
       <c r="S83" s="20" t="inlineStr">
@@ -44418,7 +44418,7 @@
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="23" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
@@ -44498,218 +44498,218 @@
       </c>
       <c r="Q84" s="19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="R84" s="19" t="inlineStr">
         <is>
-          <t>-0.300 pp</t>
+          <t>-0.270 pp</t>
         </is>
       </c>
       <c r="S84" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.760 pp</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.160 pp</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.730 pp</t>
         </is>
       </c>
       <c r="G85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.250 pp</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.050 pp</t>
         </is>
       </c>
       <c r="K85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.220 pp</t>
         </is>
       </c>
       <c r="M85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O85" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="O85" s="9" t="inlineStr">
+        <is>
+          <t>+0.470 pp</t>
         </is>
       </c>
       <c r="P85" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.100 pp</t>
         </is>
       </c>
       <c r="Q85" s="20" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R85" s="20" t="inlineStr">
         <is>
-          <t>-0.270 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S85" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="23" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C86" s="19" t="inlineStr">
         <is>
-          <t>-0.760 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D86" s="19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P86" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q86" s="19" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="R86" s="19" t="inlineStr">
+        <is>
           <t>-0.160 pp</t>
         </is>
       </c>
-      <c r="E86" s="19" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="F86" s="19" t="inlineStr">
-        <is>
-          <t>-0.730 pp</t>
-        </is>
-      </c>
-      <c r="G86" s="19" t="inlineStr">
-        <is>
-          <t>-0.050 pp</t>
-        </is>
-      </c>
-      <c r="H86" s="19" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
-      </c>
-      <c r="I86" s="19" t="inlineStr">
-        <is>
-          <t>-0.250 pp</t>
-        </is>
-      </c>
-      <c r="J86" s="19" t="inlineStr">
-        <is>
-          <t>+0.050 pp</t>
-        </is>
-      </c>
-      <c r="K86" s="19" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="L86" s="19" t="inlineStr">
-        <is>
-          <t>+0.220 pp</t>
-        </is>
-      </c>
-      <c r="M86" s="19" t="inlineStr">
-        <is>
-          <t>+0.100 pp</t>
-        </is>
-      </c>
-      <c r="N86" s="19" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="O86" s="9" t="inlineStr">
-        <is>
-          <t>+0.470 pp</t>
-        </is>
-      </c>
-      <c r="P86" s="19" t="inlineStr">
-        <is>
-          <t>+0.100 pp</t>
-        </is>
-      </c>
-      <c r="Q86" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R86" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="S86" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="23" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B87" s="20" t="inlineStr">
@@ -44789,24 +44789,24 @@
       </c>
       <c r="Q87" s="20" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="R87" s="20" t="inlineStr">
         <is>
-          <t>-0.160 pp</t>
+          <t>-0.040 pp</t>
         </is>
       </c>
       <c r="S87" s="20" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B88" s="19" t="inlineStr">
@@ -44886,24 +44886,24 @@
       </c>
       <c r="Q88" s="19" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="R88" s="19" t="inlineStr">
         <is>
-          <t>-0.040 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
       <c r="S88" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="23" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B89" s="20" t="inlineStr">
@@ -44983,24 +44983,24 @@
       </c>
       <c r="Q89" s="20" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="R89" s="20" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>-0.160 pp</t>
         </is>
       </c>
       <c r="S89" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="23" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B90" s="19" t="inlineStr">
@@ -45080,12 +45080,12 @@
       </c>
       <c r="Q90" s="19" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="R90" s="19" t="inlineStr">
         <is>
-          <t>-0.160 pp</t>
+          <t>-0.150 pp</t>
         </is>
       </c>
       <c r="S90" s="19" t="inlineStr">
@@ -45097,201 +45097,201 @@
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.730 pp</t>
         </is>
       </c>
       <c r="G91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="H91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.420 pp</t>
         </is>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="K91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="M91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O91" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="O91" s="9" t="inlineStr">
+        <is>
+          <t>+0.320 pp</t>
         </is>
       </c>
       <c r="P91" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="Q91" s="20" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R91" s="20" t="inlineStr">
         <is>
-          <t>-0.150 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S91" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="23" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B92" s="19" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C92" s="19" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D92" s="19" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
         <is>
-          <t>-0.730 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G92" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H92" s="19" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I92" s="19" t="inlineStr">
         <is>
-          <t>-0.420 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J92" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K92" s="19" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L92" s="19" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M92" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="O92" s="9" t="inlineStr">
-        <is>
-          <t>+0.320 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O92" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P92" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q92" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="R92" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.110 pp</t>
         </is>
       </c>
       <c r="S92" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="23" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B93" s="20" t="inlineStr">
@@ -45371,24 +45371,24 @@
       </c>
       <c r="Q93" s="20" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="R93" s="20" t="inlineStr">
         <is>
-          <t>-0.110 pp</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="S93" s="20" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="23" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B94" s="19" t="inlineStr">
@@ -45468,24 +45468,24 @@
       </c>
       <c r="Q94" s="19" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="R94" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="S94" s="19" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="23" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B95" s="20" t="inlineStr">
@@ -45565,218 +45565,218 @@
       </c>
       <c r="Q95" s="20" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="R95" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="S95" s="20" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="23" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="C96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="F96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.740 pp</t>
         </is>
       </c>
       <c r="G96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.070 pp</t>
         </is>
       </c>
       <c r="H96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.320 pp</t>
         </is>
       </c>
       <c r="J96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="K96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="L96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.080 pp</t>
         </is>
       </c>
       <c r="M96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O96" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="O96" s="9" t="inlineStr">
+        <is>
+          <t>+0.410 pp</t>
         </is>
       </c>
       <c r="P96" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="Q96" s="19" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R96" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S96" s="19" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B97" s="20" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C97" s="20" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
         <is>
-          <t>-0.740 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G97" s="20" t="inlineStr">
         <is>
-          <t>-0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H97" s="20" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>-0.320 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J97" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K97" s="20" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
-          <t>+0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M97" s="20" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="O97" s="9" t="inlineStr">
-        <is>
-          <t>+0.410 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O97" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P97" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="R97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.130 pp</t>
         </is>
       </c>
       <c r="S97" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B98" s="19" t="inlineStr">
@@ -45856,24 +45856,24 @@
       </c>
       <c r="Q98" s="19" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="R98" s="19" t="inlineStr">
         <is>
-          <t>-0.130 pp</t>
+          <t>-0.170 pp</t>
         </is>
       </c>
       <c r="S98" s="19" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>-0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="23" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B99" s="20" t="inlineStr">
@@ -45953,24 +45953,24 @@
       </c>
       <c r="Q99" s="20" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="R99" s="20" t="inlineStr">
         <is>
-          <t>-0.170 pp</t>
+          <t>-0.220 pp</t>
         </is>
       </c>
       <c r="S99" s="20" t="inlineStr">
         <is>
-          <t>-0.020 pp</t>
+          <t>-0.080 pp</t>
         </is>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="23" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B100" s="19" t="inlineStr">
@@ -46050,218 +46050,218 @@
       </c>
       <c r="Q100" s="19" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="R100" s="19" t="inlineStr">
         <is>
-          <t>-0.220 pp</t>
+          <t>-0.210 pp</t>
         </is>
       </c>
       <c r="S100" s="19" t="inlineStr">
         <is>
-          <t>-0.080 pp</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="C101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.260 pp</t>
         </is>
       </c>
       <c r="G101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.240 pp</t>
         </is>
       </c>
       <c r="H101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.120 pp</t>
         </is>
       </c>
       <c r="K101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="L101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.250 pp</t>
         </is>
       </c>
       <c r="M101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.090 pp</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O101" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="O101" s="9" t="inlineStr">
+        <is>
+          <t>+0.220 pp</t>
         </is>
       </c>
       <c r="P101" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="Q101" s="20" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R101" s="20" t="inlineStr">
         <is>
-          <t>-0.210 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S101" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="23" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B102" s="19" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C102" s="19" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D102" s="19" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E102" s="19" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
-          <t>-0.260 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
-          <t>+0.240 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I102" s="19" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J102" s="19" t="inlineStr">
         <is>
-          <t>+0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K102" s="19" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L102" s="19" t="inlineStr">
         <is>
-          <t>+0.250 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M102" s="19" t="inlineStr">
         <is>
-          <t>+0.090 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="O102" s="9" t="inlineStr">
-        <is>
-          <t>+0.220 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O102" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P102" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.220 pp</t>
         </is>
       </c>
       <c r="S102" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B103" s="20" t="inlineStr">
@@ -46341,24 +46341,24 @@
       </c>
       <c r="Q103" s="20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="R103" s="20" t="inlineStr">
         <is>
-          <t>-0.220 pp</t>
+          <t>-0.100 pp</t>
         </is>
       </c>
       <c r="S103" s="20" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>+0.110 pp</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B104" s="19" t="inlineStr">
@@ -46438,12 +46438,12 @@
       </c>
       <c r="Q104" s="19" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="R104" s="19" t="inlineStr">
         <is>
-          <t>-0.100 pp</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="S104" s="19" t="inlineStr">
@@ -46455,7 +46455,7 @@
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B105" s="20" t="inlineStr">
@@ -46535,218 +46535,218 @@
       </c>
       <c r="Q105" s="20" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="R105" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>+0.230 pp</t>
         </is>
       </c>
       <c r="S105" s="20" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="C106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.690 pp</t>
         </is>
       </c>
       <c r="D106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.000 pp</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
       <c r="G106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.090 pp</t>
         </is>
       </c>
       <c r="H106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="I106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
       <c r="J106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="K106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="L106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="M106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O106" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="O106" s="9" t="inlineStr">
+        <is>
+          <t>+0.020 pp</t>
         </is>
       </c>
       <c r="P106" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="Q106" s="19" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R106" s="19" t="inlineStr">
         <is>
-          <t>+0.230 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S106" s="19" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C107" s="20" t="inlineStr">
         <is>
-          <t>-0.690 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
         <is>
-          <t>+0.000 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G107" s="20" t="inlineStr">
         <is>
-          <t>+0.090 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H107" s="20" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K107" s="20" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M107" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="O107" s="9" t="inlineStr">
-        <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O107" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P107" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="R107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="S107" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.080 pp</t>
         </is>
       </c>
     </row>
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B108" s="19" t="inlineStr">
@@ -46826,24 +46826,24 @@
       </c>
       <c r="Q108" s="19" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="R108" s="19" t="inlineStr">
         <is>
-          <t>+0.300 pp</t>
+          <t>+0.310 pp</t>
         </is>
       </c>
       <c r="S108" s="19" t="inlineStr">
         <is>
-          <t>+0.080 pp</t>
+          <t>-0.090 pp</t>
         </is>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B109" s="20" t="inlineStr">
@@ -46923,24 +46923,24 @@
       </c>
       <c r="Q109" s="20" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="R109" s="20" t="inlineStr">
         <is>
-          <t>+0.310 pp</t>
+          <t>+0.210 pp</t>
         </is>
       </c>
       <c r="S109" s="20" t="inlineStr">
         <is>
-          <t>-0.090 pp</t>
+          <t>-0.070 pp</t>
         </is>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B110" s="19" t="inlineStr">
@@ -47020,12 +47020,12 @@
       </c>
       <c r="Q110" s="19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="R110" s="19" t="inlineStr">
         <is>
-          <t>+0.210 pp</t>
+          <t>+0.130 pp</t>
         </is>
       </c>
       <c r="S110" s="19" t="inlineStr">
@@ -47037,7 +47037,7 @@
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B111" s="20" t="inlineStr">
@@ -47117,218 +47117,218 @@
       </c>
       <c r="Q111" s="20" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="R111" s="20" t="inlineStr">
         <is>
-          <t>+0.130 pp</t>
+          <t>+0.190 pp</t>
         </is>
       </c>
       <c r="S111" s="20" t="inlineStr">
         <is>
-          <t>-0.070 pp</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="C112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.700 pp</t>
         </is>
       </c>
       <c r="D112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.080 pp</t>
         </is>
       </c>
       <c r="G112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.200 pp</t>
         </is>
       </c>
       <c r="H112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="I112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
       <c r="J112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.160 pp</t>
         </is>
       </c>
       <c r="K112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="L112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.130 pp</t>
         </is>
       </c>
       <c r="M112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.120 pp</t>
         </is>
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O112" s="19" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
+          <t>-0.010 pp</t>
         </is>
       </c>
       <c r="P112" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.030 pp</t>
         </is>
       </c>
       <c r="Q112" s="19" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R112" s="19" t="inlineStr">
         <is>
-          <t>+0.190 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S112" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C113" s="20" t="inlineStr">
         <is>
-          <t>-0.700 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
         <is>
-          <t>+0.080 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G113" s="20" t="inlineStr">
         <is>
-          <t>+0.200 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H113" s="20" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>+0.060 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
         <is>
-          <t>+0.160 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K113" s="20" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L113" s="20" t="inlineStr">
         <is>
-          <t>+0.130 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M113" s="20" t="inlineStr">
         <is>
-          <t>+0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
         <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="O113" s="6" t="inlineStr">
-        <is>
-          <t>-0.010 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O113" s="20" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P113" s="20" t="inlineStr">
         <is>
-          <t>-0.030 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q113" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="R113" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.280 pp</t>
         </is>
       </c>
       <c r="S113" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
     </row>
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="23" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B114" s="19" t="inlineStr">
@@ -47408,24 +47408,24 @@
       </c>
       <c r="Q114" s="19" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="R114" s="19" t="inlineStr">
         <is>
-          <t>+0.280 pp</t>
+          <t>+0.350 pp</t>
         </is>
       </c>
       <c r="S114" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>-0.010 pp</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B115" s="20" t="inlineStr">
@@ -47505,24 +47505,24 @@
       </c>
       <c r="Q115" s="20" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="R115" s="20" t="inlineStr">
         <is>
-          <t>+0.350 pp</t>
+          <t>+0.530 pp</t>
         </is>
       </c>
       <c r="S115" s="20" t="inlineStr">
         <is>
-          <t>-0.010 pp</t>
+          <t>+0.150 pp</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="23" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B116" s="19" t="inlineStr">
@@ -47602,7 +47602,7 @@
       </c>
       <c r="Q116" s="19" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="R116" s="19" t="inlineStr">
@@ -47612,14 +47612,14 @@
       </c>
       <c r="S116" s="19" t="inlineStr">
         <is>
-          <t>+0.150 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B117" s="20" t="inlineStr">
@@ -47639,84 +47639,84 @@
       </c>
       <c r="E117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.230 pp</t>
         </is>
       </c>
       <c r="G117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.120 pp</t>
         </is>
       </c>
       <c r="H117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.110 pp</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.010 pp</t>
         </is>
       </c>
       <c r="K117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="L117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.070 pp</t>
         </is>
       </c>
       <c r="M117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.070 pp</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O117" s="20" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="O117" s="6" t="inlineStr">
+        <is>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="P117" s="20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.120 pp</t>
         </is>
       </c>
       <c r="Q117" s="20" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R117" s="20" t="inlineStr">
         <is>
-          <t>+0.530 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S117" s="20" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B118" s="19" t="inlineStr">
@@ -47736,84 +47736,84 @@
       </c>
       <c r="E118" s="19" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
-          <t>+0.230 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G118" s="19" t="inlineStr">
         <is>
-          <t>+0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H118" s="19" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I118" s="19" t="inlineStr">
         <is>
-          <t>+0.110 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J118" s="19" t="inlineStr">
         <is>
-          <t>+0.010 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K118" s="19" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L118" s="19" t="inlineStr">
         <is>
-          <t>+0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M118" s="19" t="inlineStr">
         <is>
-          <t>-0.070 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="O118" s="6" t="inlineStr">
-        <is>
-          <t>-0.120 pp</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O118" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="P118" s="19" t="inlineStr">
         <is>
-          <t>-0.120 pp</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="R118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+0.370 pp</t>
         </is>
       </c>
       <c r="S118" s="19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B119" s="20" t="inlineStr">
@@ -47893,24 +47893,24 @@
       </c>
       <c r="Q119" s="20" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="R119" s="20" t="inlineStr">
         <is>
-          <t>+0.370 pp</t>
+          <t>+0.300 pp</t>
         </is>
       </c>
       <c r="S119" s="20" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>+0.040 pp</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="23" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B120" s="19" t="inlineStr">
@@ -47990,24 +47990,24 @@
       </c>
       <c r="Q120" s="19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="R120" s="19" t="inlineStr">
         <is>
-          <t>+0.300 pp</t>
+          <t>+0.090 pp</t>
         </is>
       </c>
       <c r="S120" s="19" t="inlineStr">
         <is>
-          <t>+0.040 pp</t>
+          <t>-0.050 pp</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B121" s="20" t="inlineStr">
@@ -48087,24 +48087,24 @@
       </c>
       <c r="Q121" s="20" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="R121" s="20" t="inlineStr">
         <is>
-          <t>+0.090 pp</t>
+          <t>+0.030 pp</t>
         </is>
       </c>
       <c r="S121" s="20" t="inlineStr">
         <is>
-          <t>-0.050 pp</t>
+          <t>+0.020 pp</t>
         </is>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B122" s="19" t="inlineStr">
@@ -48184,24 +48184,24 @@
       </c>
       <c r="Q122" s="19" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="R122" s="19" t="inlineStr">
         <is>
-          <t>+0.030 pp</t>
+          <t>+0.060 pp</t>
         </is>
       </c>
       <c r="S122" s="19" t="inlineStr">
         <is>
-          <t>+0.020 pp</t>
+          <t>-0.060 pp</t>
         </is>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B123" s="20" t="inlineStr">
@@ -48281,17 +48281,17 @@
       </c>
       <c r="Q123" s="20" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="R123" s="20" t="inlineStr">
         <is>
+          <t>+0.190 pp</t>
+        </is>
+      </c>
+      <c r="S123" s="20" t="inlineStr">
+        <is>
           <t>+0.060 pp</t>
-        </is>
-      </c>
-      <c r="S123" s="20" t="inlineStr">
-        <is>
-          <t>-0.060 pp</t>
         </is>
       </c>
     </row>
@@ -48336,7 +48336,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>💭 信心指數　歷史數據　　生成時間：2026-07-09 15:40 UTC</t>
+          <t>💭 信心指數　歷史數據　　生成時間：2026-07-09 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -56513,7 +56513,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>⚠️ 信用與違約　歷史數據　　生成時間：2026-07-09 15:40 UTC</t>
+          <t>⚠️ 信用與違約　歷史數據　　生成時間：2026-07-09 23:46 UTC</t>
         </is>
       </c>
     </row>
@@ -59662,7 +59662,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>🏠 房市　歷史數據　　生成時間：2026-07-09 15:40 UTC</t>
+          <t>🏠 房市　歷史數據　　生成時間：2026-07-09 23:46 UTC</t>
         </is>
       </c>
     </row>
